--- a/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_7.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_7.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>bounds_narrow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>427</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -936,34 +936,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.333607577420155</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>clear_post-origin_amplification</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.333607577420155</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>clear_post-origin_amplification</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>first_local_origin</t>
@@ -976,7 +976,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.12195121951219512</t>
+          <t>0.14634146341463414</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>bounds_narrow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>bounds_narrow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>427</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6426,34 +6426,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.333607577420155</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>clear_post-origin_amplification</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.333607577420155</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>clear_post-origin_amplification</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>first_local_origin</t>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.12195121951219512</t>
+          <t>0.14634146341463414</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>bounds_narrow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>bounds_narrow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11896,17 +11896,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>427</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11916,34 +11916,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.333607577420155</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>clear_post-origin_amplification</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.333607577420155</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>clear_post-origin_amplification</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>first_local_origin</t>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.12195121951219512</t>
+          <t>0.14634146341463414</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>bounds_narrow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
